--- a/Student_List_All_Classes.xlsx
+++ b/Student_List_All_Classes.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI27"/>
+  <dimension ref="A1:AI28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1717,6 +1717,36 @@
       <c r="AI27" t="inlineStr">
         <is>
           <t>class_1/class-1-ramdev-suthar.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>HEMA RATAWA</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>DINESH KUMAR RATAWA</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>ARCHANA DEVI</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>14/12/2019</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>class_1/class-1-hema.jpg</t>
         </is>
       </c>
     </row>

--- a/Student_List_All_Classes.xlsx
+++ b/Student_List_All_Classes.xlsx
@@ -4068,7 +4068,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI19"/>
+  <dimension ref="A1:AI24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5172,6 +5172,276 @@
       <c r="AI19" t="inlineStr">
         <is>
           <t>class_4_5/class-4-praveena.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>DINDAYAL</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>SANWAR MAL</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>SUNITA DEVI</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>02/01/2017</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>9</v>
+      </c>
+      <c r="H20" t="n">
+        <v>5</v>
+      </c>
+      <c r="I20" t="n">
+        <v>8</v>
+      </c>
+      <c r="J20" t="n">
+        <v>6</v>
+      </c>
+      <c r="K20" t="n">
+        <v>10</v>
+      </c>
+      <c r="L20" t="n">
+        <v>6</v>
+      </c>
+      <c r="M20" t="n">
+        <v>10</v>
+      </c>
+      <c r="N20" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>class_4_5/class-5-dindayal.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>DINESH SIMAR</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>MOHANRAM MEGHWAL</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>SAROJ DEVI</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>02/01/2018</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>8</v>
+      </c>
+      <c r="H21" t="n">
+        <v>9</v>
+      </c>
+      <c r="I21" t="n">
+        <v>8</v>
+      </c>
+      <c r="J21" t="n">
+        <v>8</v>
+      </c>
+      <c r="K21" t="n">
+        <v>10</v>
+      </c>
+      <c r="L21" t="n">
+        <v>6</v>
+      </c>
+      <c r="M21" t="n">
+        <v>8</v>
+      </c>
+      <c r="N21" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>class_4_5/class-5-dinesh-simar.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>KAUSHALYA</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>RAKESH</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>ANURADHA</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>14/12/2016</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>10</v>
+      </c>
+      <c r="H22" t="n">
+        <v>10</v>
+      </c>
+      <c r="I22" t="n">
+        <v>10</v>
+      </c>
+      <c r="J22" t="n">
+        <v>5</v>
+      </c>
+      <c r="K22" t="n">
+        <v>10</v>
+      </c>
+      <c r="L22" t="n">
+        <v>9</v>
+      </c>
+      <c r="M22" t="n">
+        <v>9</v>
+      </c>
+      <c r="N22" t="n">
+        <v>10</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>class_4_5/class-5-kaushalya.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>MANISHA</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>MEGHARAM NEHARA</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>MANGI DEVI</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>29/04/2015</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>6</v>
+      </c>
+      <c r="H23" t="n">
+        <v>7</v>
+      </c>
+      <c r="I23" t="n">
+        <v>9</v>
+      </c>
+      <c r="J23" t="n">
+        <v>3</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3</v>
+      </c>
+      <c r="L23" t="n">
+        <v>4</v>
+      </c>
+      <c r="M23" t="n">
+        <v>5</v>
+      </c>
+      <c r="N23" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>class_4_5/class-5-manisha.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>NAVEEN SIMAR</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>BHANI RAM</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>RUKAMANI DEVI</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>04/10/2016</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>10</v>
+      </c>
+      <c r="H24" t="n">
+        <v>9</v>
+      </c>
+      <c r="I24" t="n">
+        <v>10</v>
+      </c>
+      <c r="J24" t="n">
+        <v>7</v>
+      </c>
+      <c r="K24" t="n">
+        <v>10</v>
+      </c>
+      <c r="L24" t="n">
+        <v>6</v>
+      </c>
+      <c r="M24" t="n">
+        <v>8</v>
+      </c>
+      <c r="N24" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>class_4_5/class-5-naveen-simar.jpg</t>
         </is>
       </c>
     </row>
@@ -5186,7 +5456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI9"/>
+  <dimension ref="A1:AI4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5372,51 +5642,51 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DINDAYAL</t>
+          <t>LAXMI</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>SANWAR MAL</t>
+          <t>RAKESH SUTHAR</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>SUNITA DEVI</t>
+          <t>CHUKI DEVI</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>02/01/2017</t>
+          <t>07/02/2015</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J2" t="n">
         <v>6</v>
       </c>
       <c r="K2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="N2" t="n">
         <v>7</v>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>class_4_5/class-5-dindayal.jpg</t>
+          <t>class_4_5/class-5-laxmi.jpg</t>
         </is>
       </c>
     </row>
@@ -5426,51 +5696,51 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DINESH SIMAR</t>
+          <t>SONAKSHI KANWAR</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MOHANRAM MEGHWAL</t>
+          <t>JITENDRA SINGH</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>SAROJ DEVI</t>
+          <t>RITU NIRWAN</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>02/01/2018</t>
+          <t>06/06/2016</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H3" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J3" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K3" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="L3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>class_4_5/class-5-dinesh-simar.jpg</t>
+          <t>class_4_5/class-5-sonakshi-kanwar.jpg</t>
         </is>
       </c>
     </row>
@@ -5480,319 +5750,49 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>KAUSHALYA</t>
+          <t>DURLABH</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>RAKESH</t>
+          <t>KAILASH SUTHAR</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ANURADHA</t>
+          <t>LALITA SUTHAR</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>14/12/2016</t>
+          <t>05/04/2016</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>10</v>
       </c>
       <c r="H4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I4" t="n">
         <v>10</v>
       </c>
       <c r="J4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AI4" t="inlineStr">
-        <is>
-          <t>class_4_5/class-5-kaushalya.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>MANISHA</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>MEGHARAM NEHARA</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>MANGI DEVI</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>29/04/2015</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>6</v>
-      </c>
-      <c r="H5" t="n">
-        <v>7</v>
-      </c>
-      <c r="I5" t="n">
-        <v>9</v>
-      </c>
-      <c r="J5" t="n">
-        <v>3</v>
-      </c>
-      <c r="K5" t="n">
-        <v>3</v>
-      </c>
-      <c r="L5" t="n">
-        <v>4</v>
-      </c>
-      <c r="M5" t="n">
-        <v>5</v>
-      </c>
-      <c r="N5" t="n">
-        <v>5</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>class_4_5/class-5-manisha.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>NAVEEN SIMAR</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>BHANI RAM</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>RUKAMANI DEVI</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>04/10/2016</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>10</v>
-      </c>
-      <c r="H6" t="n">
-        <v>9</v>
-      </c>
-      <c r="I6" t="n">
-        <v>10</v>
-      </c>
-      <c r="J6" t="n">
-        <v>7</v>
-      </c>
-      <c r="K6" t="n">
-        <v>10</v>
-      </c>
-      <c r="L6" t="n">
-        <v>6</v>
-      </c>
-      <c r="M6" t="n">
-        <v>8</v>
-      </c>
-      <c r="N6" t="n">
-        <v>7</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>class_4_5/class-5-naveen-simar.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>LAXMI</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>RAKESH SUTHAR</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>CHUKI DEVI</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>07/02/2015</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>7</v>
-      </c>
-      <c r="H7" t="n">
-        <v>9</v>
-      </c>
-      <c r="I7" t="n">
-        <v>10</v>
-      </c>
-      <c r="J7" t="n">
-        <v>6</v>
-      </c>
-      <c r="K7" t="n">
-        <v>8</v>
-      </c>
-      <c r="L7" t="n">
-        <v>5</v>
-      </c>
-      <c r="M7" t="n">
-        <v>7</v>
-      </c>
-      <c r="N7" t="n">
-        <v>7</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>class_4_5/class-5-laxmi.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>SONAKSHI KANWAR</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>JITENDRA SINGH</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>RITU NIRWAN</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>06/06/2016</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>9</v>
-      </c>
-      <c r="H8" t="n">
-        <v>2</v>
-      </c>
-      <c r="I8" t="n">
-        <v>10</v>
-      </c>
-      <c r="J8" t="n">
-        <v>3</v>
-      </c>
-      <c r="K8" t="n">
-        <v>7</v>
-      </c>
-      <c r="L8" t="n">
-        <v>3</v>
-      </c>
-      <c r="M8" t="n">
-        <v>7</v>
-      </c>
-      <c r="N8" t="n">
-        <v>6</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>class_4_5/class-5-sonakshi-kanwar.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>DURLABH</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>KAILASH SUTHAR</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>LALITA SUTHAR</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>05/04/2016</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>10</v>
-      </c>
-      <c r="H9" t="n">
-        <v>9</v>
-      </c>
-      <c r="I9" t="n">
-        <v>10</v>
-      </c>
-      <c r="J9" t="n">
-        <v>7</v>
-      </c>
-      <c r="K9" t="n">
-        <v>9</v>
-      </c>
-      <c r="L9" t="n">
-        <v>7</v>
-      </c>
-      <c r="M9" t="n">
-        <v>10</v>
-      </c>
-      <c r="N9" t="n">
-        <v>8</v>
-      </c>
-      <c r="AI9" t="inlineStr">
         <is>
           <t>class_4_5/class-5-durlabh.jpg</t>
         </is>
